--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ddcdb3995a6747af/Área de Trabalho/Site mãe/catalogo-delicias-da-jac/catalogo/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ddcdb3995a6747af/Documentos/GitHub/delicias-da-jac/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_8B5E55CD87374238437138EC867B9DD418F3F6D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F929FE0B-C722-4FC7-A6D7-71E5CFDC2096}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_8B5E55CD87374238437138EC867B9DD418F3F6D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49C77072-E207-4E2F-B49E-891C461AC6C8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2041,7 +2041,10 @@
         <v>79</v>
       </c>
       <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
+      <c r="L2" s="5" t="str">
+        <f>A2&amp;".png"</f>
+        <v>macaron-individual.png</v>
+      </c>
       <c r="M2" s="5" t="s">
         <v>80</v>
       </c>
@@ -2098,7 +2101,10 @@
         <v>91</v>
       </c>
       <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
+      <c r="L3" s="5" t="str">
+        <f t="shared" ref="L3:L19" si="0">A3&amp;".png"</f>
+        <v>macaron-caixinha.png</v>
+      </c>
       <c r="M3" s="5" t="s">
         <v>80</v>
       </c>
@@ -2154,8 +2160,8 @@
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5" t="str">
-        <f>A4</f>
-        <v>macaron-torre</v>
+        <f t="shared" si="0"/>
+        <v>macaron-torre.png</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>80</v>
@@ -2218,8 +2224,8 @@
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="5" t="str">
-        <f t="shared" ref="L5:L19" si="0">A5</f>
-        <v>pirulito-simples</v>
+        <f t="shared" si="0"/>
+        <v>pirulito-simples.png</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
@@ -2277,7 +2283,7 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>pirulito-modelado-simples</v>
+        <v>pirulito-modelado-simples.png</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -2339,7 +2345,7 @@
       <c r="K7" s="5"/>
       <c r="L7" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>pirulito-modelado-premium</v>
+        <v>pirulito-modelado-premium.png</v>
       </c>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
@@ -2401,7 +2407,7 @@
       <c r="K8" s="5"/>
       <c r="L8" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>pirulito-brigadeiro</v>
+        <v>pirulito-brigadeiro.png</v>
       </c>
       <c r="M8" s="5" t="s">
         <v>121</v>
@@ -2453,7 +2459,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>lembrancinha-mini-suspiros</v>
+        <v>lembrancinha-mini-suspiros.png</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
@@ -2505,7 +2511,7 @@
       <c r="K10" s="5"/>
       <c r="L10" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>lembrancinha-rosa</v>
+        <v>lembrancinha-rosa.png</v>
       </c>
       <c r="M10" s="5" t="s">
         <v>121</v>
@@ -2565,7 +2571,7 @@
       <c r="K11" s="5"/>
       <c r="L11" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>lembrancinha-bonequinha</v>
+        <v>lembrancinha-bonequinha.png</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>121</v>
@@ -2625,7 +2631,7 @@
       <c r="K12" s="5"/>
       <c r="L12" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>lembrancinha-adicional</v>
+        <v>lembrancinha-adicional.png</v>
       </c>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
@@ -2677,7 +2683,7 @@
       <c r="K13" s="5"/>
       <c r="L13" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>suspiro-modelado</v>
+        <v>suspiro-modelado.png</v>
       </c>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
@@ -2733,7 +2739,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>suspiro-3d</v>
+        <v>suspiro-3d.png</v>
       </c>
       <c r="M14" s="5" t="s">
         <v>150</v>
@@ -2793,7 +2799,7 @@
       <c r="K15" s="5"/>
       <c r="L15" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>centro-de-mesa</v>
+        <v>centro-de-mesa.png</v>
       </c>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
@@ -2845,7 +2851,7 @@
       <c r="K16" s="5"/>
       <c r="L16" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>torre-de-suspiros</v>
+        <v>torre-de-suspiros.png</v>
       </c>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
@@ -2905,7 +2911,7 @@
       </c>
       <c r="L17" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>mini-suspiros</v>
+        <v>mini-suspiros.png</v>
       </c>
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
@@ -2955,7 +2961,7 @@
       <c r="K18" s="5"/>
       <c r="L18" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>brownie</v>
+        <v>brownie.png</v>
       </c>
       <c r="M18" s="5" t="s">
         <v>173</v>
@@ -3007,7 +3013,7 @@
       <c r="K19" s="5"/>
       <c r="L19" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>bem-casado</v>
+        <v>bem-casado.png</v>
       </c>
       <c r="M19" s="5" t="s">
         <v>178</v>

--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ddcdb3995a6747af/Área de Trabalho/Site mãe/catalogo-delicias-da-jac/catalogo/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ddcdb3995a6747af/Documentos/GitHub/delicias-da-jac/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_8B5E55CD87374238437138EC867B9DD418F3F6D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F929FE0B-C722-4FC7-A6D7-71E5CFDC2096}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_8B5E55CD87374238437138EC867B9DD418F3F6D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56BF5913-244F-4EBF-B7CE-5842C6421C6E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2041,7 +2041,10 @@
         <v>79</v>
       </c>
       <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
+      <c r="L2" s="5" t="str">
+        <f>A2&amp;".png"</f>
+        <v>macaron-individual.png</v>
+      </c>
       <c r="M2" s="5" t="s">
         <v>80</v>
       </c>
@@ -2098,7 +2101,10 @@
         <v>91</v>
       </c>
       <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
+      <c r="L3" s="5" t="str">
+        <f>A3&amp;".png"</f>
+        <v>macaron-caixinha.png</v>
+      </c>
       <c r="M3" s="5" t="s">
         <v>80</v>
       </c>
@@ -2154,8 +2160,8 @@
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5" t="str">
-        <f>A4</f>
-        <v>macaron-torre</v>
+        <f t="shared" ref="L4:L19" si="0">A4&amp;".png"</f>
+        <v>macaron-torre.png</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>80</v>
@@ -2218,8 +2224,8 @@
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="5" t="str">
-        <f t="shared" ref="L5:L19" si="0">A5</f>
-        <v>pirulito-simples</v>
+        <f t="shared" si="0"/>
+        <v>pirulito-simples.png</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
@@ -2277,7 +2283,7 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>pirulito-modelado-simples</v>
+        <v>pirulito-modelado-simples.png</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -2339,7 +2345,7 @@
       <c r="K7" s="5"/>
       <c r="L7" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>pirulito-modelado-premium</v>
+        <v>pirulito-modelado-premium.png</v>
       </c>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
@@ -2401,7 +2407,7 @@
       <c r="K8" s="5"/>
       <c r="L8" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>pirulito-brigadeiro</v>
+        <v>pirulito-brigadeiro.png</v>
       </c>
       <c r="M8" s="5" t="s">
         <v>121</v>
@@ -2453,7 +2459,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>lembrancinha-mini-suspiros</v>
+        <v>lembrancinha-mini-suspiros.png</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
@@ -2505,7 +2511,7 @@
       <c r="K10" s="5"/>
       <c r="L10" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>lembrancinha-rosa</v>
+        <v>lembrancinha-rosa.png</v>
       </c>
       <c r="M10" s="5" t="s">
         <v>121</v>
@@ -2565,7 +2571,7 @@
       <c r="K11" s="5"/>
       <c r="L11" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>lembrancinha-bonequinha</v>
+        <v>lembrancinha-bonequinha.png</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>121</v>
@@ -2625,7 +2631,7 @@
       <c r="K12" s="5"/>
       <c r="L12" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>lembrancinha-adicional</v>
+        <v>lembrancinha-adicional.png</v>
       </c>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
@@ -2677,7 +2683,7 @@
       <c r="K13" s="5"/>
       <c r="L13" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>suspiro-modelado</v>
+        <v>suspiro-modelado.png</v>
       </c>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
@@ -2733,7 +2739,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>suspiro-3d</v>
+        <v>suspiro-3d.png</v>
       </c>
       <c r="M14" s="5" t="s">
         <v>150</v>
@@ -2793,7 +2799,7 @@
       <c r="K15" s="5"/>
       <c r="L15" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>centro-de-mesa</v>
+        <v>centro-de-mesa.png</v>
       </c>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
@@ -2845,7 +2851,7 @@
       <c r="K16" s="5"/>
       <c r="L16" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>torre-de-suspiros</v>
+        <v>torre-de-suspiros.png</v>
       </c>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
@@ -2905,7 +2911,7 @@
       </c>
       <c r="L17" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>mini-suspiros</v>
+        <v>mini-suspiros.png</v>
       </c>
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
@@ -2955,7 +2961,7 @@
       <c r="K18" s="5"/>
       <c r="L18" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>brownie</v>
+        <v>brownie.png</v>
       </c>
       <c r="M18" s="5" t="s">
         <v>173</v>
@@ -3007,7 +3013,7 @@
       <c r="K19" s="5"/>
       <c r="L19" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>bem-casado</v>
+        <v>bem-casado.png</v>
       </c>
       <c r="M19" s="5" t="s">
         <v>178</v>

--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ddcdb3995a6747af/Documentos/GitHub/delicias-da-jac/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_8B5E55CD87374238437138EC867B9DD418F3F6D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56BF5913-244F-4EBF-B7CE-5842C6421C6E}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_B94A672F2620A2788D999A37CE41865D87E5F9B3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68FE58CD-AE55-4B5E-875E-773651237C28}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Leia-me" sheetId="1" r:id="rId1"/>
@@ -31,25 +31,36 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Temas!$A$1:$A$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Variações!$A$1:$N$36</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Sistema</author>
+  </authors>
+  <commentList>
+    <comment ref="B18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Deixe VAZIO enquanto o sistema de encomendas não estiver publicado (o site continua enviando o pedido pelo WhatsApp). Depois de publicar o Apps Script, cole aqui o endereço do aplicativo web: https://script.google.com/macros/s/.../exec</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="357">
   <si>
     <t>COMO USAR ESTA PLANILHA</t>
   </si>
@@ -1104,6 +1115,9 @@
     <t>Catálogo 2026, páginas 1–19</t>
   </si>
   <si>
+    <t>Sistema de encomendas (URL do Apps Script)</t>
+  </si>
+  <si>
     <t>Parágrafo</t>
   </si>
   <si>
@@ -1114,6 +1128,9 @@
   </si>
   <si>
     <t>Nossa missão é oferecer atendimento de excelência e encantar os convidados por meio de doces artesanais.</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbzYTEcM6CsepahQodXVdxLfoniWyuK3jR0cMtyKtu5ij0_Fhezup8gbzQWafbM8Ydmo/exec</t>
   </si>
 </sst>
 </file>
@@ -2041,10 +2058,7 @@
         <v>79</v>
       </c>
       <c r="K2" s="5"/>
-      <c r="L2" s="5" t="str">
-        <f>A2&amp;".png"</f>
-        <v>macaron-individual.png</v>
-      </c>
+      <c r="L2" s="5"/>
       <c r="M2" s="5" t="s">
         <v>80</v>
       </c>
@@ -2101,10 +2115,7 @@
         <v>91</v>
       </c>
       <c r="K3" s="5"/>
-      <c r="L3" s="5" t="str">
-        <f>A3&amp;".png"</f>
-        <v>macaron-caixinha.png</v>
-      </c>
+      <c r="L3" s="5"/>
       <c r="M3" s="5" t="s">
         <v>80</v>
       </c>
@@ -2159,10 +2170,7 @@
         <v>99</v>
       </c>
       <c r="K4" s="5"/>
-      <c r="L4" s="5" t="str">
-        <f t="shared" ref="L4:L19" si="0">A4&amp;".png"</f>
-        <v>macaron-torre.png</v>
-      </c>
+      <c r="L4" s="5"/>
       <c r="M4" s="5" t="s">
         <v>80</v>
       </c>
@@ -2223,10 +2231,7 @@
         <v>106</v>
       </c>
       <c r="K5" s="5"/>
-      <c r="L5" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>pirulito-simples.png</v>
-      </c>
+      <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
@@ -2281,10 +2286,7 @@
         <v>106</v>
       </c>
       <c r="K6" s="5"/>
-      <c r="L6" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>pirulito-modelado-simples.png</v>
-      </c>
+      <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
@@ -2343,10 +2345,7 @@
         <v>106</v>
       </c>
       <c r="K7" s="5"/>
-      <c r="L7" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>pirulito-modelado-premium.png</v>
-      </c>
+      <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
@@ -2405,10 +2404,7 @@
         <v>106</v>
       </c>
       <c r="K8" s="5"/>
-      <c r="L8" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>pirulito-brigadeiro.png</v>
-      </c>
+      <c r="L8" s="5"/>
       <c r="M8" s="5" t="s">
         <v>121</v>
       </c>
@@ -2457,10 +2453,7 @@
         <v>106</v>
       </c>
       <c r="K9" s="5"/>
-      <c r="L9" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>lembrancinha-mini-suspiros.png</v>
-      </c>
+      <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
@@ -2509,10 +2502,7 @@
         <v>106</v>
       </c>
       <c r="K10" s="5"/>
-      <c r="L10" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>lembrancinha-rosa.png</v>
-      </c>
+      <c r="L10" s="5"/>
       <c r="M10" s="5" t="s">
         <v>121</v>
       </c>
@@ -2569,10 +2559,7 @@
         <v>106</v>
       </c>
       <c r="K11" s="5"/>
-      <c r="L11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>lembrancinha-bonequinha.png</v>
-      </c>
+      <c r="L11" s="5"/>
       <c r="M11" s="5" t="s">
         <v>121</v>
       </c>
@@ -2629,10 +2616,7 @@
         <v>140</v>
       </c>
       <c r="K12" s="5"/>
-      <c r="L12" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>lembrancinha-adicional.png</v>
-      </c>
+      <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
@@ -2681,10 +2665,7 @@
         <v>106</v>
       </c>
       <c r="K13" s="5"/>
-      <c r="L13" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>suspiro-modelado.png</v>
-      </c>
+      <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
@@ -2737,10 +2718,7 @@
         <v>106</v>
       </c>
       <c r="K14" s="5"/>
-      <c r="L14" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>suspiro-3d.png</v>
-      </c>
+      <c r="L14" s="5"/>
       <c r="M14" s="5" t="s">
         <v>150</v>
       </c>
@@ -2797,10 +2775,7 @@
         <v>106</v>
       </c>
       <c r="K15" s="5"/>
-      <c r="L15" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>centro-de-mesa.png</v>
-      </c>
+      <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
@@ -2849,10 +2824,7 @@
         <v>99</v>
       </c>
       <c r="K16" s="5"/>
-      <c r="L16" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>torre-de-suspiros.png</v>
-      </c>
+      <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
@@ -2909,10 +2881,7 @@
       <c r="K17" s="5">
         <v>250</v>
       </c>
-      <c r="L17" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>mini-suspiros.png</v>
-      </c>
+      <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
@@ -2959,10 +2928,7 @@
         <v>106</v>
       </c>
       <c r="K18" s="5"/>
-      <c r="L18" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>brownie.png</v>
-      </c>
+      <c r="L18" s="5"/>
       <c r="M18" s="5" t="s">
         <v>173</v>
       </c>
@@ -3011,10 +2977,7 @@
         <v>106</v>
       </c>
       <c r="K19" s="5"/>
-      <c r="L19" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>bem-casado.png</v>
-      </c>
+      <c r="L19" s="5"/>
       <c r="M19" s="5" t="s">
         <v>178</v>
       </c>
@@ -3039,7 +3002,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:W19" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <dataValidations disablePrompts="1" count="2">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="S2:S300 V2:W300" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
@@ -3050,7 +3013,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
             <xm:f>Categorias!$B$2:$B$40</xm:f>
@@ -4620,8 +4583,8 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -4764,9 +4727,18 @@
         <v>350</v>
       </c>
     </row>
+    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>356</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B17" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4780,22 +4752,22 @@
   <sheetData>
     <row r="1" spans="1:1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>

--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ddcdb3995a6747af/Documentos/GitHub/delicias-da-jac/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_B94A672F2620A2788D999A37CE41865D87E5F9B3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68FE58CD-AE55-4B5E-875E-773651237C28}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_B94A672F2620A2788D999A37CE41865D87E5F9B3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F172724E-BE0E-47AF-9B34-2F78793BB5AA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Leia-me" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,20 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Temas!$A$1:$A$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Variações!$A$1:$N$36</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2058,7 +2071,10 @@
         <v>79</v>
       </c>
       <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
+      <c r="L2" s="5" t="str">
+        <f>A2&amp;".png"</f>
+        <v>macaron-individual.png</v>
+      </c>
       <c r="M2" s="5" t="s">
         <v>80</v>
       </c>
@@ -2115,7 +2131,10 @@
         <v>91</v>
       </c>
       <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
+      <c r="L3" s="5" t="str">
+        <f t="shared" ref="L3:L19" si="0">A3&amp;".png"</f>
+        <v>macaron-caixinha.png</v>
+      </c>
       <c r="M3" s="5" t="s">
         <v>80</v>
       </c>
@@ -2170,7 +2189,10 @@
         <v>99</v>
       </c>
       <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
+      <c r="L4" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>macaron-torre.png</v>
+      </c>
       <c r="M4" s="5" t="s">
         <v>80</v>
       </c>
@@ -2231,7 +2253,10 @@
         <v>106</v>
       </c>
       <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
+      <c r="L5" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>pirulito-simples.png</v>
+      </c>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
@@ -2286,7 +2311,10 @@
         <v>106</v>
       </c>
       <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
+      <c r="L6" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>pirulito-modelado-simples.png</v>
+      </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
@@ -2345,7 +2373,10 @@
         <v>106</v>
       </c>
       <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
+      <c r="L7" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>pirulito-modelado-premium.png</v>
+      </c>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
@@ -2404,7 +2435,10 @@
         <v>106</v>
       </c>
       <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
+      <c r="L8" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>pirulito-brigadeiro.png</v>
+      </c>
       <c r="M8" s="5" t="s">
         <v>121</v>
       </c>
@@ -2453,7 +2487,10 @@
         <v>106</v>
       </c>
       <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
+      <c r="L9" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>lembrancinha-mini-suspiros.png</v>
+      </c>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
@@ -2502,7 +2539,10 @@
         <v>106</v>
       </c>
       <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
+      <c r="L10" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>lembrancinha-rosa.png</v>
+      </c>
       <c r="M10" s="5" t="s">
         <v>121</v>
       </c>
@@ -2559,7 +2599,10 @@
         <v>106</v>
       </c>
       <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
+      <c r="L11" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>lembrancinha-bonequinha.png</v>
+      </c>
       <c r="M11" s="5" t="s">
         <v>121</v>
       </c>
@@ -2616,7 +2659,10 @@
         <v>140</v>
       </c>
       <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
+      <c r="L12" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>lembrancinha-adicional.png</v>
+      </c>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
@@ -2665,7 +2711,10 @@
         <v>106</v>
       </c>
       <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
+      <c r="L13" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>suspiro-modelado.png</v>
+      </c>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
@@ -2718,7 +2767,10 @@
         <v>106</v>
       </c>
       <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
+      <c r="L14" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>suspiro-3d.png</v>
+      </c>
       <c r="M14" s="5" t="s">
         <v>150</v>
       </c>
@@ -2775,7 +2827,10 @@
         <v>106</v>
       </c>
       <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
+      <c r="L15" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>centro-de-mesa.png</v>
+      </c>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
@@ -2824,7 +2879,10 @@
         <v>99</v>
       </c>
       <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
+      <c r="L16" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>torre-de-suspiros.png</v>
+      </c>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
@@ -2881,7 +2939,10 @@
       <c r="K17" s="5">
         <v>250</v>
       </c>
-      <c r="L17" s="5"/>
+      <c r="L17" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>mini-suspiros.png</v>
+      </c>
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
@@ -2928,7 +2989,10 @@
         <v>106</v>
       </c>
       <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
+      <c r="L18" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>brownie.png</v>
+      </c>
       <c r="M18" s="5" t="s">
         <v>173</v>
       </c>
@@ -2977,7 +3041,10 @@
         <v>106</v>
       </c>
       <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
+      <c r="L19" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>bem-casado.png</v>
+      </c>
       <c r="M19" s="5" t="s">
         <v>178</v>
       </c>
